--- a/lab1.xlsx
+++ b/lab1.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="Medicion_directa" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Medicion_indirecta" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="progresivo" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Medicion_continua" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Escalon" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
